--- a/users.xlsx
+++ b/users.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,60 +659,6 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Andrew Moore</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>andrew</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>acoole123</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Store</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Wais Rahimi</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>wais1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>wais123</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Team Member</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Accounts</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/users.xlsx
+++ b/users.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,6 +659,33 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Super Admin</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>admin123</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Super Admin</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>System Administration</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/users.xlsx
+++ b/users.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,26 @@
           <t>dept</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>can_view_all_dept</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>can_generate_pdf</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>can_download_data</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>can_approve_requests</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -469,6 +489,18 @@
           <t>National Grid</t>
         </is>
       </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -496,6 +528,18 @@
           <t>Isolator</t>
         </is>
       </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -523,6 +567,18 @@
           <t>Project</t>
         </is>
       </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -550,6 +606,18 @@
           <t>Accounts</t>
         </is>
       </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -577,6 +645,18 @@
           <t>ACoole Electrical Ltd</t>
         </is>
       </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -604,6 +684,18 @@
           <t>System Administration</t>
         </is>
       </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -631,6 +723,18 @@
           <t>Payroll Department</t>
         </is>
       </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -658,32 +762,56 @@
           <t>Accounts</t>
         </is>
       </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>acoole123</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>Super Admin</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>admin123</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Super Admin</t>
-        </is>
-      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>System Administration</t>
-        </is>
+          <t>System Administrator</t>
+        </is>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/users.xlsx
+++ b/users.xlsx
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="F6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -778,17 +778,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>acoole123</t>
+          <t>acoole2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">

--- a/users.xlsx
+++ b/users.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Denise Nunn</t>
+          <t>National Grid Manager</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -544,7 +544,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Amber Cox</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -622,7 +622,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Andy Coole</t>
+          <t>Andy Acoole</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -646,29 +646,29 @@
         </is>
       </c>
       <c r="F6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>wais</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>wais</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>superadmin123</t>
@@ -681,26 +681,26 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>System Administration</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="F7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Wais Rahimi</t>
+          <t>Payroll Team</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -720,14 +720,14 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Payroll Department</t>
+          <t>Accounts</t>
         </is>
       </c>
       <c r="F8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
@@ -739,78 +739,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Millie Sabin</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>millie</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sabin123</t>
+          <t>Acoole2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Super Admin</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Accounts</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="F9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>acoole2026</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Super Admin</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>System Administrator</t>
-        </is>
-      </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="b">
         <v>1</v>
       </c>
     </row>
